--- a/Unsorted/Павловск/до войны/павловск_до войны_подписи.xlsx
+++ b/Unsorted/Павловск/до войны/павловск_до войны_подписи.xlsx
@@ -38,26 +38,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Вид фасадов дворца с юго-западной стороны.1920-е - 1930-е гг., г. Павловск
-Автор съемки не установлено
-ЦГАКФФД СПб. Оп. 1ДР-14. Ед.хр.11875
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Фасад дворца со стороны Парадного двора. 1920-1930-ее гг., г. Павловск
 Автор съемки: Не установлен 
 ЦГАКФФД СПб. Оп. ДР-14. Ед.хр.11876
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Розовый павильон. Июнь 1933 г., г. Павловск
-Автор съемки: Бамунер
-ЦГАКФФД СПб. Оп/ 1ГР-53. Ед.хр.81299
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">г. Павловск. Бывшая Павловская крепость, переданная для детдома «Смена» Пригородного РИКа. Март 1935 г., г. Павловск. Автор съемки: Малов
-ЦГАКФФД СПб. Оп. 1БР-3. Ед.хр.2431
 </t>
   </si>
   <si>
@@ -93,12 +76,53 @@
   <si>
     <t>Павловский дворец. Дворовый фасад, 1935 г Семенов В. №20137</t>
   </si>
+  <si>
+    <t xml:space="preserve">г. Павловск. Бывшая Павловская крепость, переданная для детдома «Смена» Пригородного РИКа. Март 1935 г., г. Павловск.  
+Автор съемки: Малов
+ЦГАКФФД СПб. Оп. 1БР-3. Ед.хр.2431
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Розовый павильон. Июнь 1933 г., г. Павловск
+Автор съемки: Бамунер
+ЦГАКФФД СПб. Оп</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1ГР-53. Ед.хр.81299
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид фасадов дворца с юго-западной стороны. 1920-е - 1930-е гг., г. Павловск
+Автор съемки не установлено
+ЦГАКФФД СПб. Оп. 1ДР-14. Ед.хр.11875
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +143,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -481,15 +513,15 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
@@ -497,45 +529,46 @@
     </row>
     <row r="6" spans="1:2" ht="57.6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="43.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unsorted/Павловск/до войны/павловск_до войны_подписи.xlsx
+++ b/Unsorted/Павловск/до войны/павловск_до войны_подписи.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>подпись</t>
   </si>
@@ -44,13 +44,6 @@
 </t>
   </si>
   <si>
-    <t>Павильон «Трех граций», построенный архитектором
-Ч. Камероном в 1800-1803 гг. Вид со стороны улицы
-Революции. 1920-е - 1930-е гг., г. Павловск
-Автор съемки не установлен
-ЦГАКФФД СПб Др 11885</t>
-  </si>
-  <si>
     <t>ЦГАКФФД СПб Бр2431</t>
   </si>
   <si>
@@ -79,43 +72,185 @@
   <si>
     <t xml:space="preserve">г. Павловск. Бывшая Павловская крепость, переданная для детдома «Смена» Пригородного РИКа. Март 1935 г., г. Павловск.  
 Автор съемки: Малов
-ЦГАКФФД СПб. Оп. 1БР-3. Ед.хр.2431
-</t>
-  </si>
-  <si>
-    <r>
-      <t>Розовый павильон. Июнь 1933 г., г. Павловск
+ЦГАКФФД СПб. Оп. 1БР-3. Ед.хр. 2431
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розовый павильон. Июнь 1933 г., г. Павловск
 Автор съемки: Бамунер
-ЦГАКФФД СПб. Оп</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 1ГР-53. Ед.хр.81299
-</t>
-    </r>
+ЦГАКФФД СПб. Оп. 1ГР-53. Ед.хр. 81299
+</t>
   </si>
   <si>
     <t xml:space="preserve">Вид фасадов дворца с юго-западной стороны. 1920-е - 1930-е гг., г. Павловск
 Автор съемки не установлено
-ЦГАКФФД СПб. Оп. 1ДР-14. Ед.хр.11875
-</t>
+ЦГАКФФД СПб. Оп. 1ДР-14. Ед.хр. 11875
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Греческий зал до 1941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Греческий зал. До 1941 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Галерея Гонзаго. Начало XX в.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Галерея Гонзаго
+Начало XX в.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Галерея Гонзаго (интерьер)
+Начало XXв.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Галерея Гонзаго (интерьер). Начало XX в.</t>
+  </si>
+  <si>
+    <t>Павильон «Трех граций», построенный архитектором Ч. Камероном в 1800-1803 гг. Вид со стороны улицы Революции.1920-е - 1930-е гг.,
+г. Павловск
+Автор съемки не установлен 
+ЦГАКФФД СПб. Оп. 1ДР-14. Ед .хр.11885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Тронный зал
+Начало XX в.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Тронный зал. Начало XX в.</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Итальянский зал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Итальянский зал
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Белая столовая (Столовая Камерона)
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Белая столовая (Столовая Камерона)</t>
+  </si>
+  <si>
+    <t>6. Павловский дворец. Итальянский зал</t>
+  </si>
+  <si>
+    <t>7. Павловский дворец. Итальянский зал (3)</t>
+  </si>
+  <si>
+    <t>8. Павловский дворец. Итальянский зал (2)</t>
+  </si>
+  <si>
+    <t>10. Павловский дворец. Белая столовая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кабинет Павла
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Кабинет Павла</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Библиотека Павла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Библиотека Павла
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кавалерский зал
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Кавалерский зал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. До 1918 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец. До 1918 г.</t>
+  </si>
+  <si>
+    <t>15. Павловский дворец. До 1918 г. (2)</t>
+  </si>
+  <si>
+    <t>Павловский дворец. До 1941 г (1930-е)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. До 1941 г (1930-е?)
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Павловский дворец</t>
+  </si>
+  <si>
+    <t>Павловский дворец (2)</t>
+  </si>
+  <si>
+    <t>Памятник Александре Павловне до 1941 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Памятник Александре Павловне. До 1941 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мавзолей Павла I. Интерьер. До 1918 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Мавзолей Павла I. Интерьер. до 1918 г.</t>
+  </si>
+  <si>
+    <t>Мавзолей Павла I. До 1941 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мавзолей Павла I. До 1941 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>Мавзолей Павла. До 1941</t>
   </si>
 </sst>
 </file>
@@ -150,10 +285,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -189,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -204,6 +337,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -476,7 +613,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -484,14 +621,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.89453125" customWidth="1"/>
+    <col min="1" max="1" width="44.9453125" customWidth="1"/>
     <col min="2" max="2" width="58.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6">
+    <row r="1" spans="1:3" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -499,11 +636,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="5"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -511,60 +648,237 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72">
+    <row r="4" spans="1:3" ht="72">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6">
+      <c r="A5" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="57.6">
-      <c r="A5" t="s">
-        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="57.6">
+    <row r="6" spans="1:3" ht="57.6">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="72">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="72">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" ht="72">
+      <c r="A8" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="72">
-      <c r="A8" t="s">
-        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="72">
+    <row r="9" spans="1:3" ht="72">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="43.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="43.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:3" ht="57.6">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="72">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="72">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="72">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="57.6">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="57.6">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="57.6">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="57.6">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="57.6">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="57.6">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="57.6">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="57.6">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="57.6">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="57.6">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="57.6">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="57.6">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="57.6">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="57.6">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="57.6">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="57.6">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="57.6">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="57.6">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
